--- a/MO.xlsx
+++ b/MO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0250B56-E2B0-457F-84C6-8860B1CE6523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F09ADCF-AD7E-4682-8FEA-3F4E68C7701A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{20CEB54E-2453-4B61-AAC7-D7D76D478430}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{20CEB54E-2453-4B61-AAC7-D7D76D478430}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Oscar Settje:</t>
         </r>
@@ -85,7 +85,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Asset Impairment</t>
@@ -132,7 +132,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Oscar Settje:</t>
         </r>
@@ -141,7 +141,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Sale of IQOS System Commercial Rigths
@@ -178,7 +178,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="143">
   <si>
     <t>Altria Group</t>
   </si>
@@ -620,7 +620,7 @@
     <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -659,19 +659,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <u/>
@@ -848,15 +835,15 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -864,10 +851,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -886,16 +873,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1274,7 +1262,7 @@
         <v>2</v>
       </c>
       <c r="M3" s="4">
-        <v>66.430000000000007</v>
+        <v>68.67</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -1285,10 +1273,10 @@
         <v>3</v>
       </c>
       <c r="M4" s="6">
-        <v>1679.8909530000001</v>
+        <v>1690.6616409999999</v>
       </c>
       <c r="N4" s="34" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -1300,7 +1288,7 @@
       </c>
       <c r="M5" s="8">
         <f>M4*M3</f>
-        <v>111595.15600779002</v>
+        <v>116097.73488747</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -1311,7 +1299,7 @@
         <v>1287</v>
       </c>
       <c r="N6" s="34" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -1326,7 +1314,7 @@
         <v>24720</v>
       </c>
       <c r="N7" s="34" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -1347,7 +1335,7 @@
       </c>
       <c r="M8" s="8">
         <f>M5+M7-M6</f>
-        <v>135028.15600779001</v>
+        <v>139530.73488747</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -14445,7 +14433,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B09457F9-C4DB-4307-8BCE-CCB612E8D1EA}">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -14668,34 +14656,57 @@
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B33" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B34" s="33" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B35" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B36" s="3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B37" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B38" s="3" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B40" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="3">
+        <v>100</v>
+      </c>
+      <c r="E40" s="3">
+        <v>89.62</v>
+      </c>
+      <c r="F40" s="3">
+        <v>111.37</v>
+      </c>
+      <c r="G40" s="3">
+        <v>116.24</v>
+      </c>
+      <c r="H40" s="3">
+        <v>112.08</v>
+      </c>
+      <c r="I40" s="3">
+        <v>157.88</v>
       </c>
     </row>
   </sheetData>
